--- a/tabtools/demo/demo_regtab.xlsx
+++ b/tabtools/demo/demo_regtab.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="916" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="916" uniqueCount="232">
   <si>
     <t>Table 2. Propensity Score Model (Logistic Regression)</t>
   </si>
@@ -492,13 +492,10 @@
     <t>Base mean model</t>
   </si>
   <si>
-    <t>0.06</t>
-  </si>
-  <si>
-    <t>-0.13</t>
-  </si>
-  <si>
-    <t>-0.57</t>
+    <t>0.88</t>
+  </si>
+  <si>
+    <t>0.56</t>
   </si>
   <si>
     <t>26,200</t>
@@ -510,16 +507,16 @@
     <t>27142.20</t>
   </si>
   <si>
-    <t>(0.01, 0.01)</t>
-  </si>
-  <si>
-    <t>(0.04, 0.08)</t>
-  </si>
-  <si>
-    <t>(-0.22, -0.03)</t>
-  </si>
-  <si>
-    <t>(-0.67, -0.48)</t>
+    <t>(1.01, 1.01)</t>
+  </si>
+  <si>
+    <t>(1.04, 1.09)</t>
+  </si>
+  <si>
+    <t>(0.80, 0.97)</t>
+  </si>
+  <si>
+    <t>(0.51, 0.62)</t>
   </si>
   <si>
     <t>0.009</t>
@@ -528,31 +525,31 @@
     <t>Adjusted mean model</t>
   </si>
   <si>
-    <t>0.08</t>
-  </si>
-  <si>
-    <t>-0.06</t>
-  </si>
-  <si>
-    <t>-0.72</t>
-  </si>
-  <si>
-    <t>0.80</t>
+    <t>1.08</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>2.23</t>
   </si>
   <si>
     <t>26596.04</t>
   </si>
   <si>
-    <t>(0.06, 0.10)</t>
-  </si>
-  <si>
-    <t>(-0.15, 0.04)</t>
-  </si>
-  <si>
-    <t>(-0.82, -0.62)</t>
-  </si>
-  <si>
-    <t>(0.68, 0.93)</t>
+    <t>(1.06, 1.11)</t>
+  </si>
+  <si>
+    <t>(0.86, 1.04)</t>
+  </si>
+  <si>
+    <t>(0.44, 0.54)</t>
+  </si>
+  <si>
+    <t>(1.97, 2.53)</t>
   </si>
   <si>
     <t>0.26</t>
@@ -640,9 +637,6 @@
   </si>
   <si>
     <t>0.007</t>
-  </si>
-  <si>
-    <t>0.88</t>
   </si>
   <si>
     <t>0.39</t>
@@ -1513,7 +1507,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>1</v>
@@ -1536,7 +1530,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="62" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D2" s="61" t="s">
         <v>1</v>
@@ -1573,10 +1567,10 @@
         <v>137</v>
       </c>
       <c r="D4" s="70" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E4" s="70" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5">
@@ -1590,10 +1584,10 @@
         <v>14</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6">
@@ -1610,7 +1604,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="70" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7">
@@ -1658,10 +1652,10 @@
         <v>78</v>
       </c>
       <c r="D9" s="70" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E9" s="70" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
@@ -1675,10 +1669,10 @@
         <v>78</v>
       </c>
       <c r="D10" s="70" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E10" s="70" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1686,7 +1680,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>1</v>
@@ -1703,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="69" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C12" s="71" t="s">
         <v>16</v>
@@ -1720,16 +1714,16 @@
         <v>1</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14">
@@ -1737,16 +1731,16 @@
         <v>1</v>
       </c>
       <c r="B14" s="69" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D14" s="70" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E14" s="70" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15">
@@ -1754,16 +1748,16 @@
         <v>1</v>
       </c>
       <c r="B15" s="69" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C15" s="70" t="s">
         <v>38</v>
       </c>
       <c r="D15" s="70" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E15" s="70" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16">
@@ -1777,10 +1771,10 @@
         <v>20</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17">
@@ -1794,10 +1788,10 @@
         <v>15</v>
       </c>
       <c r="D17" s="70" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E17" s="70" t="s">
-        <v>205</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18">
@@ -1808,10 +1802,10 @@
         <v>10</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>94</v>
@@ -1828,10 +1822,10 @@
         <v>137</v>
       </c>
       <c r="D19" s="73" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E19" s="73" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -1858,7 +1852,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>1</v>
@@ -1881,7 +1875,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
@@ -1918,10 +1912,10 @@
         <v>137</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5">
@@ -1932,13 +1926,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="E5" s="44" t="s">
         <v>209</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="E5" s="44" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="6">
@@ -1955,7 +1949,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7">
@@ -1966,18 +1960,18 @@
         <v>8</v>
       </c>
       <c r="C7" s="46" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E7" s="47" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="78" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C8" s="0"/>
       <c r="D8" s="0"/>
@@ -2006,7 +2000,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>1</v>
@@ -2029,7 +2023,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
@@ -2066,10 +2060,10 @@
         <v>137</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5">
@@ -2117,10 +2111,10 @@
         <v>20</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8">
@@ -2137,7 +2131,7 @@
         <v>24</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9">
@@ -2148,10 +2142,10 @@
         <v>10</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E9" s="44" t="s">
         <v>94</v>
@@ -2168,15 +2162,15 @@
         <v>137</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="78" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C11" s="0"/>
       <c r="D11" s="0"/>
@@ -2206,7 +2200,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>1</v>
@@ -2229,7 +2223,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
@@ -2266,10 +2260,10 @@
         <v>137</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5">
@@ -2280,13 +2274,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6">
@@ -2303,7 +2297,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7">
@@ -2314,13 +2308,13 @@
         <v>8</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8">
@@ -2334,10 +2328,10 @@
         <v>19</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9">
@@ -2345,10 +2339,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D9" s="51" t="s">
         <v>1</v>
@@ -2362,10 +2356,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C10" s="53" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D10" s="46" t="s">
         <v>1</v>
@@ -2376,7 +2370,7 @@
     </row>
     <row r="11">
       <c r="B11" s="78" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C11" s="0"/>
       <c r="D11" s="0"/>
@@ -4345,10 +4339,10 @@
     <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
     <col min="2" max="2" width="24.7109375" style="1" customWidth="true"/>
     <col min="3" max="3" width="8.2109375" style="1" customWidth="true"/>
-    <col min="4" max="4" width="14.2109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="12.2109375" style="1" customWidth="true"/>
     <col min="5" max="5" width="7.7109375" style="1" customWidth="true"/>
     <col min="6" max="6" width="8.2109375" style="1" customWidth="true"/>
-    <col min="7" max="7" width="14.2109375" style="1" customWidth="true"/>
+    <col min="7" max="7" width="12.2109375" style="1" customWidth="true"/>
     <col min="8" max="8" width="7.7109375" style="1" customWidth="true"/>
   </cols>
   <sheetData>
@@ -4395,7 +4389,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>1</v>
@@ -4412,7 +4406,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>22</v>
@@ -4421,7 +4415,7 @@
         <v>31</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="G3" s="31" t="s">
         <v>22</v>
@@ -4438,19 +4432,19 @@
         <v>148</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E4" s="44" t="s">
         <v>94</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H4" s="44" t="s">
         <v>94</v>
@@ -4464,19 +4458,19 @@
         <v>149</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E5" s="44" t="s">
         <v>94</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H5" s="44" t="s">
         <v>94</v>
@@ -4490,22 +4484,22 @@
         <v>150</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H6" s="44" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7">
@@ -4516,19 +4510,19 @@
         <v>151</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E7" s="44" t="s">
         <v>94</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H7" s="44" t="s">
         <v>94</v>
@@ -4551,10 +4545,10 @@
         <v>1</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H8" s="44" t="s">
         <v>94</v>
@@ -4568,7 +4562,7 @@
         <v>54</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D9" s="51" t="s">
         <v>1</v>
@@ -4577,7 +4571,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G9" s="51" t="s">
         <v>1</v>
@@ -4594,7 +4588,7 @@
         <v>101</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>1</v>
@@ -4603,7 +4597,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G10" s="16" t="s">
         <v>1</v>
@@ -4620,7 +4614,7 @@
         <v>153</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D11" s="46" t="s">
         <v>1</v>
@@ -4629,7 +4623,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="53" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G11" s="46" t="s">
         <v>1</v>

--- a/tabtools/demo/demo_regtab.xlsx
+++ b/tabtools/demo/demo_regtab.xlsx
@@ -727,7 +727,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="12">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -737,53 +737,39 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <i/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
-      <b/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
+      <sz val="12"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <i/>
+      <color rgb="FFA0A0A0"/>
       <name val="Arial"/>
     </font>
     <font>
+      <i/>
       <sz val="10"/>
-      <name val="Arial"/>
       <color rgb="FFA0A0A0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <i/>
-      <name val="Arial"/>
-      <color rgb="FFA0A0A0"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Arial"/>
     </font>
     <font>
+      <i/>
       <sz val="8"/>
       <name val="Arial"/>
-      <i/>
     </font>
   </fonts>
   <fills count="2">
@@ -794,7 +780,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -804,445 +790,289 @@
     </border>
     <border/>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <left/>
       <right style="thin"/>
       <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="medium"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="medium"/>
       <bottom style="medium"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1264,223 +1094,223 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="26" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="27" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="31" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="42" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="42" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="42" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="44" t="s">
+      <c r="C6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="42" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="44" t="s">
+      <c r="D7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="42" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="42" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="42" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="42" t="s">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="42" t="s">
+      <c r="A12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="43" t="s">
+      <c r="A13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="47" t="s">
+      <c r="E13" s="9" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1506,325 +1336,325 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="62" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="61" t="s">
+      <c r="D2" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="29" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="65" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="65" t="s">
+      <c r="D3" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="65" t="s">
+      <c r="E3" s="37" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="69" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="D4" s="70" t="s">
+      <c r="D4" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="E4" s="70" t="s">
+      <c r="E4" s="30" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="6" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="69" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="70" t="s">
+      <c r="E6" s="30" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="69" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="70" t="s">
+      <c r="C7" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="30" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="69" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="71" t="s">
+      <c r="C8" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="70" t="s">
+      <c r="D8" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="30" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="69" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="70" t="s">
+      <c r="C9" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="D9" s="70" t="s">
+      <c r="D9" s="30" t="s">
         <v>188</v>
       </c>
-      <c r="E9" s="70" t="s">
+      <c r="E9" s="30" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="69" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="70" t="s">
+      <c r="D10" s="30" t="s">
         <v>189</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="30" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="32" t="s">
         <v>177</v>
       </c>
-      <c r="C11" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="16" t="s">
+      <c r="C11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="69" t="s">
+      <c r="A12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="C12" s="71" t="s">
+      <c r="C12" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="70" t="s">
+      <c r="D12" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="30" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="A13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="6" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="69" t="s">
+      <c r="A14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="C14" s="70" t="s">
+      <c r="C14" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="D14" s="70" t="s">
+      <c r="D14" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="E14" s="70" t="s">
+      <c r="E14" s="30" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="69" t="s">
+      <c r="A15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="70" t="s">
+      <c r="D15" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="E15" s="70" t="s">
+      <c r="E15" s="30" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="A16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="6" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="69" t="s">
+      <c r="A17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="70" t="s">
+      <c r="C17" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="70" t="s">
+      <c r="D17" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="E17" s="70" t="s">
+      <c r="E17" s="30" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="6" t="s">
+      <c r="A18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="6" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="72" t="s">
+      <c r="A19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="73" t="s">
+      <c r="C19" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="D19" s="73" t="s">
+      <c r="D19" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="E19" s="73" t="s">
+      <c r="E19" s="31" t="s">
         <v>204</v>
       </c>
     </row>
@@ -1851,126 +1681,126 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="26" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="D2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="27" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="31" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="42" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="42" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="7" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="42" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="7" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="43" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="9" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="78" t="s">
+      <c r="B8" s="39" t="s">
         <v>212</v>
       </c>
       <c r="C8" s="0"/>
@@ -1999,177 +1829,177 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="26" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="D2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="27" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="31" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="42" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="42" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="44" t="s">
+      <c r="C5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="42" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="44" t="s">
+      <c r="D6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="42" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="E7" s="44" t="s">
+      <c r="E7" s="7" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="42" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="7" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="42" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="43" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D10" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="E10" s="47" t="s">
+      <c r="E10" s="9" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="78" t="s">
+      <c r="B11" s="39" t="s">
         <v>217</v>
       </c>
       <c r="C11" s="0"/>
@@ -2199,177 +2029,177 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="61" t="s">
         <v>218</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="60" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="26" t="s">
+      <c r="A2" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="59" t="s">
         <v>221</v>
       </c>
-      <c r="D2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="27" t="s">
+      <c r="D2" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="43" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="31" t="s">
+      <c r="A3" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="58" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="42" t="s">
+      <c r="A4" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="47" t="s">
         <v>137</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="48" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="42" t="s">
+      <c r="A5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="47" t="s">
         <v>207</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="47" t="s">
         <v>187</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="48" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="42" t="s">
+      <c r="A6" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="48" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="42" t="s">
+      <c r="A7" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="47" t="s">
         <v>222</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="47" t="s">
         <v>225</v>
       </c>
-      <c r="E7" s="44" t="s">
+      <c r="E7" s="48" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="42" t="s">
+      <c r="A8" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="47" t="s">
         <v>226</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="48" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="48" t="s">
+      <c r="A9" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="55" t="s">
         <v>219</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="46" t="s">
         <v>223</v>
       </c>
       <c r="D9" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="E9" s="54" t="s">
+      <c r="E9" s="52" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="43" t="s">
+      <c r="A10" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="54" t="s">
         <v>220</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="D10" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="47" t="s">
+      <c r="D10" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="50" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="78" t="s">
+      <c r="B11" s="40" t="s">
         <v>231</v>
       </c>
       <c r="C11" s="0"/>
@@ -2399,184 +2229,184 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="26" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="31" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="42" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="42" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="42" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="44" t="s">
+      <c r="C6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="42" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="42" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="44" t="s">
+      <c r="D8" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="42" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="44" t="s">
+      <c r="D9" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="42" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="42" t="s">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="44" t="s">
+      <c r="D11" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="42" t="s">
+      <c r="A12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="43" t="s">
+      <c r="A13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="47" t="s">
+      <c r="D13" s="9" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2601,184 +2431,184 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="26" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="31" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="42" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="42" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="42" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="44" t="s">
+      <c r="C6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="42" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="42" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="44" t="s">
+      <c r="D8" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="42" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="44" t="s">
+      <c r="D9" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="42" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="7" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="42" t="s">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="44" t="s">
+      <c r="D11" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="42" t="s">
+      <c r="A12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="43" t="s">
+      <c r="A13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="47" t="s">
+      <c r="D13" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2810,562 +2640,562 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="8" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="26" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="26" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="26" t="s">
+      <c r="G2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="27" t="s">
+      <c r="J2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="31" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="31" t="s">
+      <c r="I3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="31" t="s">
+      <c r="J3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="42" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="H4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="44" t="s">
+      <c r="K4" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="42" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="H5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="44" t="s">
+      <c r="K5" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="42" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="44" t="s">
+      <c r="C6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="42" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="45" t="s">
+      <c r="C7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="45" t="s">
+      <c r="G7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="44" t="s">
+      <c r="J7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="42" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="16" t="s">
+      <c r="C8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="44" t="s">
+      <c r="H8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="16" t="s">
+      <c r="J8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="44" t="s">
+      <c r="K8" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="42" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="16" t="s">
+      <c r="C9" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="44" t="s">
+      <c r="H9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="I9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="J9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="44" t="s">
+      <c r="K9" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="42" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="16" t="s">
+      <c r="C10" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="H10" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="16" t="s">
+      <c r="I10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="16" t="s">
+      <c r="J10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K10" s="44" t="s">
+      <c r="K10" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="42" t="s">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="16" t="s">
+      <c r="C11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="J11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K11" s="44" t="s">
+      <c r="K11" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="42" t="s">
+      <c r="A12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="16" t="s">
+      <c r="C12" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="16" t="s">
+      <c r="J12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="K12" s="44" t="s">
+      <c r="K12" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="42" t="s">
+      <c r="A13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="16" t="s">
+      <c r="C13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="16" t="s">
+      <c r="J13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="K13" s="44" t="s">
+      <c r="K13" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="48" t="s">
+      <c r="A14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="52" t="s">
+      <c r="D14" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="G14" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="I14" s="52" t="s">
+      <c r="G14" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="J14" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="54" t="s">
+      <c r="J14" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="42" t="s">
+      <c r="A15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="17" t="s">
+      <c r="D15" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="G15" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="I15" s="17" t="s">
+      <c r="G15" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="J15" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="44" t="s">
+      <c r="J15" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="43" t="s">
+      <c r="A16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="53" t="s">
+      <c r="C16" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="53" t="s">
+      <c r="D16" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="G16" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="53" t="s">
+      <c r="G16" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="J16" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="47" t="s">
+      <c r="J16" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="9" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3403,257 +3233,257 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="26" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="27" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="31" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="42" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="7" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="42" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="42" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="7" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="42" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="44" t="s">
+      <c r="C7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="42" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="44" t="s">
+      <c r="D8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="42" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="7" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="42" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="7" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="42" t="s">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="42" t="s">
+      <c r="A12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="42" t="s">
+      <c r="A13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="44" t="s">
+      <c r="E13" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="48" t="s">
+      <c r="A14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" s="54" t="s">
+      <c r="D14" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="43" t="s">
+      <c r="A15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="53" t="s">
+      <c r="C15" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="47" t="s">
+      <c r="D15" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3681,223 +3511,223 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="26" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="27" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="31" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="42" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="42" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="7" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="42" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="42" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E7" s="44" t="s">
+      <c r="E7" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="48" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="C8" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="E8" s="54" t="s">
+      <c r="E8" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="42" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="48" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="54" t="s">
+      <c r="D10" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="42" t="s">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="44" t="s">
+      <c r="D11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="42" t="s">
+      <c r="A12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="D12" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="44" t="s">
+      <c r="D12" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="43" t="s">
+      <c r="A13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="47" t="s">
+      <c r="D13" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3926,206 +3756,206 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="26" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="D2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="27" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="31" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="42" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="42" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="42" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="44" t="s">
+      <c r="C6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="42" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="44" t="s">
+      <c r="D7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="42" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="42" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="42" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="42" t="s">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="7" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="55" t="s">
+      <c r="A12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="60" t="s">
+      <c r="D12" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="27" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4152,172 +3982,172 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="26" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="27" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="31" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="42" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="7" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="42" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="42" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="42" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="E7" s="44" t="s">
+      <c r="E7" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="42" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="48" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="54" t="s">
+      <c r="D9" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="43" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="D10" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="47" t="s">
+      <c r="D10" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4347,288 +4177,288 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="26" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="D2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="26" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="G2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="27" t="s">
+      <c r="G2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="31" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="42" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="H4" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="42" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="H5" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="42" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="42" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E7" s="44" t="s">
+      <c r="E7" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="H7" s="44" t="s">
+      <c r="H7" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="42" t="s">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="16" t="s">
+      <c r="C8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="H8" s="44" t="s">
+      <c r="H8" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="48" t="s">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="D9" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="52" t="s">
+      <c r="D9" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="G9" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="54" t="s">
+      <c r="G9" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="42" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="D10" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="17" t="s">
+      <c r="D10" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="G10" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="44" t="s">
+      <c r="G10" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="43" t="s">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="D11" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="53" t="s">
+      <c r="D11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="G11" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="47" t="s">
+      <c r="G11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>1</v>
       </c>
     </row>

--- a/tabtools/demo/demo_regtab.xlsx
+++ b/tabtools/demo/demo_regtab.xlsx
@@ -19,13 +19,18 @@
     <sheet name="Regtab Select" sheetId="11" r:id="rId13"/>
     <sheet name="Regtab Drop" sheetId="12" r:id="rId14"/>
     <sheet name="Regtab AddRow" sheetId="13" r:id="rId15"/>
+    <sheet name="Regtab cformat" sheetId="14" r:id="rId16"/>
+    <sheet name="Flat Reftop" sheetId="15" r:id="rId17"/>
+    <sheet name="Transpose" sheetId="16" r:id="rId18"/>
+    <sheet name="Cell Note" sheetId="17" r:id="rId19"/>
+    <sheet name="Fit Counts" sheetId="18" r:id="rId20"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="916" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1225" uniqueCount="311">
   <si>
     <t>Table 2. Propensity Score Model (Logistic Regression)</t>
   </si>
@@ -69,658 +74,895 @@
     <t>OR</t>
   </si>
   <si>
+    <t>1.05</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>8.27</t>
+  </si>
+  <si>
+    <t>7.07</t>
+  </si>
+  <si>
+    <t>1.02</t>
+  </si>
+  <si>
+    <t>1.13</t>
+  </si>
+  <si>
+    <t>95% CI</t>
+  </si>
+  <si>
+    <t>(1.05, 1.05)</t>
+  </si>
+  <si>
+    <t>(0.69, 0.81)</t>
+  </si>
+  <si>
+    <t>(0.86, 1.06)</t>
+  </si>
+  <si>
+    <t>(7.59, 9.03)</t>
+  </si>
+  <si>
+    <t>(6.48, 7.71)</t>
+  </si>
+  <si>
+    <t>(0.93, 1.12)</t>
+  </si>
+  <si>
+    <t>(1.04, 1.22)</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
+  <si>
+    <t>&lt;0.001</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>0.68</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>Table 2a. Compact Propensity Score Model</t>
+  </si>
+  <si>
+    <t>Compact</t>
+  </si>
+  <si>
+    <t>OR 95% CI</t>
+  </si>
+  <si>
+    <t>1.05 (1.05, 1.05)</t>
+  </si>
+  <si>
+    <t>0.75 (0.69, 0.81)</t>
+  </si>
+  <si>
+    <t>0.95 (0.86, 1.06)</t>
+  </si>
+  <si>
+    <t>8.27 (7.59, 9.03)</t>
+  </si>
+  <si>
+    <t>7.07 (6.48, 7.71)</t>
+  </si>
+  <si>
+    <t>1.02 (0.93, 1.12)</t>
+  </si>
+  <si>
+    <t>1.13 (1.04, 1.22)</t>
+  </si>
+  <si>
+    <t>Table 2b. Propensity Score Model without P-values</t>
+  </si>
+  <si>
+    <t>No p-value</t>
+  </si>
+  <si>
+    <t>Table 3. Propensity Score Models -- Nested Comparison</t>
+  </si>
+  <si>
+    <t>Observations</t>
+  </si>
+  <si>
+    <t>AIC</t>
+  </si>
+  <si>
+    <t>BIC</t>
+  </si>
+  <si>
+    <t>Demographics</t>
+  </si>
+  <si>
+    <t>1.04</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>15,000</t>
+  </si>
+  <si>
+    <t>19418.82</t>
+  </si>
+  <si>
+    <t>19441.67</t>
+  </si>
+  <si>
+    <t>(1.03, 1.04)</t>
+  </si>
+  <si>
+    <t>(0.75, 0.86)</t>
+  </si>
+  <si>
+    <t>+ Comorbidities</t>
+  </si>
+  <si>
+    <t>8.37</t>
+  </si>
+  <si>
+    <t>7.15</t>
+  </si>
+  <si>
+    <t>14234.84</t>
+  </si>
+  <si>
+    <t>14288.15</t>
+  </si>
+  <si>
+    <t>(7.68, 9.12)</t>
+  </si>
+  <si>
+    <t>(6.56, 7.79)</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>Full Model</t>
+  </si>
+  <si>
+    <t>14230.35</t>
+  </si>
+  <si>
+    <t>14298.89</t>
+  </si>
+  <si>
+    <t>Table 4. Cox Proportional Hazards Model</t>
+  </si>
+  <si>
+    <t>Treatment group</t>
+  </si>
+  <si>
+    <t>Subjects</t>
+  </si>
+  <si>
+    <t>Log-likelihood</t>
+  </si>
+  <si>
+    <t>Cox PH</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
     <t>1.00</t>
   </si>
   <si>
-    <t>0.99</t>
-  </si>
-  <si>
-    <t>Reference</t>
-  </si>
-  <si>
-    <t>1.02</t>
+    <t>1.06</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
+    <t>1.48</t>
+  </si>
+  <si>
+    <t>1.69</t>
+  </si>
+  <si>
+    <t>-43574.97</t>
+  </si>
+  <si>
+    <t>(0.97, 1.12)</t>
+  </si>
+  <si>
+    <t>(1.00, 1.00)</t>
+  </si>
+  <si>
+    <t>(0.96, 1.07)</t>
+  </si>
+  <si>
+    <t>(0.99, 1.14)</t>
+  </si>
+  <si>
+    <t>(1.42, 1.60)</t>
+  </si>
+  <si>
+    <t>(1.40, 1.57)</t>
+  </si>
+  <si>
+    <t>(1.59, 1.80)</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>0.11</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>0.080</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>Table 5. Mixed Effects Model -- BP Change by Region</t>
+  </si>
+  <si>
+    <t>Age (years)</t>
+  </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>Variance: Healthcare Region (Intercept)</t>
+  </si>
+  <si>
+    <t>Residual Variance</t>
+  </si>
+  <si>
+    <t>Groups</t>
+  </si>
+  <si>
+    <t>ICC</t>
+  </si>
+  <si>
+    <t>Mixed</t>
+  </si>
+  <si>
+    <t>Coef.</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>-0.19</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>2.76</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>1690.23</t>
+  </si>
+  <si>
+    <t>0.006</t>
+  </si>
+  <si>
+    <t>(0.00, 0.01)</t>
+  </si>
+  <si>
+    <t>(-0.35, -0.04)</t>
+  </si>
+  <si>
+    <t>(0.06, 0.09)</t>
+  </si>
+  <si>
+    <t>(2.21, 3.32)</t>
+  </si>
+  <si>
+    <t>(0.00, 0.12)</t>
+  </si>
+  <si>
+    <t>(0.85, 1.07)</t>
+  </si>
+  <si>
+    <t>0.010</t>
+  </si>
+  <si>
+    <t>0.016</t>
+  </si>
+  <si>
+    <t>Table 5a. CDISC-Format Regression Output</t>
+  </si>
+  <si>
+    <t>CDISC</t>
+  </si>
+  <si>
+    <t>1.0505</t>
+  </si>
+  <si>
+    <t>0.7481</t>
+  </si>
+  <si>
+    <t>0.9526</t>
+  </si>
+  <si>
+    <t>8.3695</t>
+  </si>
+  <si>
+    <t>7.1504</t>
+  </si>
+  <si>
+    <t>(1.0470, 1.0539)</t>
+  </si>
+  <si>
+    <t>(0.6886, 0.8126)</t>
+  </si>
+  <si>
+    <t>(0.8593, 1.0561)</t>
+  </si>
+  <si>
+    <t>(0.8571, 1.0588)</t>
+  </si>
+  <si>
+    <t>(7.6781, 9.1233)</t>
+  </si>
+  <si>
+    <t>(6.5607, 7.7931)</t>
+  </si>
+  <si>
+    <t>Table 5b. Poisson Regression -- Incidence Rate Ratios</t>
+  </si>
+  <si>
+    <t>Poisson</t>
+  </si>
+  <si>
+    <t>IRR</t>
+  </si>
+  <si>
+    <t>1.01</t>
+  </si>
+  <si>
+    <t>1.26</t>
+  </si>
+  <si>
+    <t>1.20</t>
+  </si>
+  <si>
+    <t>21215.55</t>
+  </si>
+  <si>
+    <t>(0.97, 1.11)</t>
+  </si>
+  <si>
+    <t>(1.18, 1.33)</t>
+  </si>
+  <si>
+    <t>(1.13, 1.27)</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>Table 5c. GEE Models -- QICu for Model Comparison</t>
+  </si>
+  <si>
+    <t>Age in current year</t>
+  </si>
+  <si>
+    <t>Current grade completed</t>
+  </si>
+  <si>
+    <t>1 if not SMSA</t>
+  </si>
+  <si>
+    <t>1 if south</t>
+  </si>
+  <si>
+    <t>Race black</t>
+  </si>
+  <si>
+    <t>QICu</t>
+  </si>
+  <si>
+    <t>Base mean model</t>
+  </si>
+  <si>
+    <t>0.88</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>26,200</t>
+  </si>
+  <si>
+    <t>4,434</t>
+  </si>
+  <si>
+    <t>27142.20</t>
+  </si>
+  <si>
+    <t>(1.01, 1.01)</t>
+  </si>
+  <si>
+    <t>(1.04, 1.09)</t>
+  </si>
+  <si>
+    <t>(0.80, 0.97)</t>
+  </si>
+  <si>
+    <t>(0.51, 0.62)</t>
+  </si>
+  <si>
+    <t>0.009</t>
+  </si>
+  <si>
+    <t>Adjusted mean model</t>
+  </si>
+  <si>
+    <t>1.08</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>2.23</t>
+  </si>
+  <si>
+    <t>26596.04</t>
+  </si>
+  <si>
+    <t>(1.06, 1.11)</t>
+  </si>
+  <si>
+    <t>(0.86, 1.04)</t>
+  </si>
+  <si>
+    <t>(0.44, 0.54)</t>
+  </si>
+  <si>
+    <t>(1.97, 2.53)</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>Table 5d. Logistic Regression with Advanced Formatting</t>
+  </si>
+  <si>
+    <t>Marital status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Single</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Married</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Divorced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Widowed</t>
+  </si>
+  <si>
+    <t>Advanced</t>
+  </si>
+  <si>
+    <t>0.91</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>1.14</t>
+  </si>
+  <si>
+    <t>1.03</t>
+  </si>
+  <si>
+    <t>(0.96, 1.14)</t>
+  </si>
+  <si>
+    <t>(0.94, 1.08)</t>
+  </si>
+  <si>
+    <t>(0.96, 1.15)</t>
+  </si>
+  <si>
+    <t>(0.84, 0.99)</t>
+  </si>
+  <si>
+    <t>(0.83, 1.01)</t>
+  </si>
+  <si>
+    <t>(0.87, 1.07)</t>
+  </si>
+  <si>
+    <t>(1.00, 1.16)</t>
+  </si>
+  <si>
+    <t>(0.91, 1.05)</t>
+  </si>
+  <si>
+    <t>(1.06, 1.23)</t>
+  </si>
+  <si>
+    <t>(0.96, 1.10)</t>
+  </si>
+  <si>
+    <t>0.074</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>0.028</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>0.049</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>Table 5e. Selected Covariates (keep/drop demo)</t>
+  </si>
+  <si>
+    <t>Selected</t>
+  </si>
+  <si>
+    <t>1.08*</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>Selected covariates from full model. * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001</t>
+  </si>
+  <si>
+    <t>Table 5f. Logistic Model (Confounders Suppressed)</t>
+  </si>
+  <si>
+    <t>Adjusted</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>Model adjusted for age, sex, and education (coefficients suppressed).</t>
+  </si>
+  <si>
+    <t>Table 5g. Logistic Regression with Custom Summary Rows</t>
+  </si>
+  <si>
+    <t>P for trend</t>
+  </si>
+  <si>
+    <t>P for interaction</t>
+  </si>
+  <si>
+    <t>Model 1</t>
+  </si>
+  <si>
+    <t>1.10*</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>(0.97, 1.14)</t>
+  </si>
+  <si>
+    <t>(1.00, 1.01)</t>
+  </si>
+  <si>
+    <t>(1.02, 1.18)</t>
+  </si>
+  <si>
+    <t>(0.92, 1.07)</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>0.017</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>Custom rows appended below model estimates. * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001</t>
+  </si>
+  <si>
+    <t>Table 2b. CV Events (Three Decimals, 'to' Intervals)</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>1.050</t>
+  </si>
+  <si>
+    <t>1.002</t>
+  </si>
+  <si>
+    <t>1.010</t>
+  </si>
+  <si>
+    <t>1.053</t>
+  </si>
+  <si>
+    <t>1.095</t>
+  </si>
+  <si>
+    <t>0.995</t>
+  </si>
+  <si>
+    <t>(0.966 to 1.143)</t>
+  </si>
+  <si>
+    <t>(1.000 to 1.005)</t>
+  </si>
+  <si>
+    <t>(0.943 to 1.081)</t>
+  </si>
+  <si>
+    <t>(0.967 to 1.147)</t>
+  </si>
+  <si>
+    <t>(0.965 to 1.149)</t>
+  </si>
+  <si>
+    <t>(1.016 to 1.180)</t>
+  </si>
+  <si>
+    <t>(0.925 to 1.071)</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>0.018</t>
+  </si>
+  <si>
+    <t>Table 2c. regtab flat frame written by puttab (reference level on top)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>1.09 (1.02, 1.17)</t>
+  </si>
+  <si>
+    <t>1.00 (1.00, 1.00)</t>
+  </si>
+  <si>
+    <t>1.01 (0.94, 1.08)</t>
+  </si>
+  <si>
+    <t>0.95 (0.87, 1.04)</t>
+  </si>
+  <si>
+    <t>1.00 (0.93, 1.08)</t>
+  </si>
+  <si>
+    <t>0.014</t>
+  </si>
+  <si>
+    <t>0.099</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>&gt;0.99</t>
+  </si>
+  <si>
+    <t>Table 2d. Treatment Odds Ratio by Model Specification</t>
+  </si>
+  <si>
+    <t>Crude</t>
+  </si>
+  <si>
+    <t>OR (95% CI)</t>
+  </si>
+  <si>
+    <t>1.11 (1.03, 1.18)</t>
+  </si>
+  <si>
+    <t>1.05 (0.97, 1.14)</t>
+  </si>
+  <si>
+    <t>Table 2e. Text in a Cell That Must Not Show an Estimate</t>
+  </si>
+  <si>
+    <t>1.11</t>
+  </si>
+  <si>
+    <t>Not in model</t>
+  </si>
+  <si>
+    <t>(1.03, 1.18)</t>
   </si>
   <si>
     <t>1.09</t>
   </si>
   <si>
-    <t>1.01</t>
-  </si>
-  <si>
-    <t>1.10</t>
-  </si>
-  <si>
-    <t>0.98</t>
-  </si>
-  <si>
-    <t>95% CI</t>
-  </si>
-  <si>
-    <t>(1.00, 1.00)</t>
-  </si>
-  <si>
-    <t>(0.93, 1.06)</t>
-  </si>
-  <si>
-    <t>(0.94, 1.11)</t>
-  </si>
-  <si>
-    <t>(1.00, 1.18)</t>
-  </si>
-  <si>
-    <t>(0.94, 1.08)</t>
-  </si>
-  <si>
-    <t>(1.03, 1.17)</t>
-  </si>
-  <si>
-    <t>(0.93, 1.08)</t>
-  </si>
-  <si>
-    <t>(0.92, 1.05)</t>
-  </si>
-  <si>
-    <t>p-value</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>0.84</t>
-  </si>
-  <si>
-    <t>0.66</t>
-  </si>
-  <si>
-    <t>0.053</t>
-  </si>
-  <si>
-    <t>0.78</t>
-  </si>
-  <si>
-    <t>0.005</t>
-  </si>
-  <si>
-    <t>0.96</t>
-  </si>
-  <si>
-    <t>0.63</t>
-  </si>
-  <si>
-    <t>Table 2a. Compact Propensity Score Model</t>
-  </si>
-  <si>
-    <t>Compact</t>
-  </si>
-  <si>
-    <t>OR 95% CI</t>
-  </si>
-  <si>
-    <t>1.00 (1.00, 1.00)</t>
-  </si>
-  <si>
-    <t>0.99 (0.93, 1.06)</t>
-  </si>
-  <si>
-    <t>1.02 (0.94, 1.11)</t>
-  </si>
-  <si>
-    <t>1.09 (1.00, 1.18)</t>
-  </si>
-  <si>
-    <t>1.01 (0.94, 1.08)</t>
-  </si>
-  <si>
-    <t>1.10 (1.03, 1.17)</t>
-  </si>
-  <si>
-    <t>1.00 (0.93, 1.08)</t>
-  </si>
-  <si>
-    <t>0.98 (0.92, 1.05)</t>
-  </si>
-  <si>
-    <t>Table 2b. Propensity Score Model without P-values</t>
-  </si>
-  <si>
-    <t>No p-value</t>
-  </si>
-  <si>
-    <t>Table 3. Propensity Score Models -- Nested Comparison</t>
-  </si>
-  <si>
-    <t>Observations</t>
-  </si>
-  <si>
-    <t>AIC</t>
-  </si>
-  <si>
-    <t>BIC</t>
-  </si>
-  <si>
-    <t>Demographics</t>
-  </si>
-  <si>
-    <t>15,000</t>
-  </si>
-  <si>
-    <t>20247.25</t>
-  </si>
-  <si>
-    <t>20270.10</t>
-  </si>
-  <si>
-    <t>0.24</t>
-  </si>
-  <si>
-    <t>0.81</t>
-  </si>
-  <si>
-    <t>+ Comorbidities</t>
-  </si>
-  <si>
-    <t>20242.79</t>
-  </si>
-  <si>
-    <t>20296.10</t>
-  </si>
-  <si>
-    <t>0.006</t>
-  </si>
-  <si>
-    <t>Full Model</t>
-  </si>
-  <si>
-    <t>20246.55</t>
-  </si>
-  <si>
-    <t>20315.09</t>
-  </si>
-  <si>
-    <t>Table 4. Cox Proportional Hazards Model</t>
-  </si>
-  <si>
-    <t>Treatment group</t>
-  </si>
-  <si>
-    <t>Subjects</t>
-  </si>
-  <si>
-    <t>Log-likelihood</t>
-  </si>
-  <si>
-    <t>Cox PH</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>1.04</t>
-  </si>
-  <si>
-    <t>1.06</t>
-  </si>
-  <si>
-    <t>1.05</t>
-  </si>
-  <si>
-    <t>1.53</t>
+    <t>(0.97, 1.15)</t>
+  </si>
+  <si>
+    <t>Table 2f. GI Bleeding by Region, Patients Aged 80+</t>
+  </si>
+  <si>
+    <t>Healthcare region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Stockholm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Uppsala/Orebro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Southeast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  North</t>
+  </si>
+  <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>People</t>
+  </si>
+  <si>
+    <t>Person-years</t>
+  </si>
+  <si>
+    <t>1.44</t>
+  </si>
+  <si>
+    <t>–</t>
+  </si>
+  <si>
+    <t>1.18</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>450</t>
+  </si>
+  <si>
+    <t>4,102</t>
+  </si>
+  <si>
+    <t>(0.68, 3.03)</t>
+  </si>
+  <si>
+    <t>(0.55, 2.38)</t>
+  </si>
+  <si>
+    <t>(0.57, 2.46)</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>0.72</t>
+  </si>
+  <si>
+    <t>0.65</t>
   </si>
   <si>
     <t>1.50</t>
   </si>
   <si>
-    <t>1.69</t>
-  </si>
-  <si>
-    <t>-43574.74</t>
-  </si>
-  <si>
-    <t>(0.98, 1.10)</t>
-  </si>
-  <si>
-    <t>(0.96, 1.07)</t>
-  </si>
-  <si>
-    <t>(0.99, 1.14)</t>
-  </si>
-  <si>
-    <t>(0.97, 1.12)</t>
-  </si>
-  <si>
-    <t>(1.45, 1.62)</t>
-  </si>
-  <si>
-    <t>(1.42, 1.59)</t>
-  </si>
-  <si>
-    <t>(1.59, 1.80)</t>
-  </si>
-  <si>
-    <t>0.17</t>
-  </si>
-  <si>
-    <t>0.65</t>
-  </si>
-  <si>
-    <t>0.077</t>
-  </si>
-  <si>
-    <t>0.22</t>
-  </si>
-  <si>
-    <t>&lt;0.001</t>
-  </si>
-  <si>
-    <t>Table 5. Mixed Effects Model -- BP Change by Region</t>
-  </si>
-  <si>
-    <t>Age (years)</t>
-  </si>
-  <si>
-    <t>BMI</t>
-  </si>
-  <si>
-    <t>Intercept</t>
-  </si>
-  <si>
-    <t>Variance: Healthcare Region (Intercept)</t>
-  </si>
-  <si>
-    <t>Residual Variance</t>
-  </si>
-  <si>
-    <t>Groups</t>
-  </si>
-  <si>
-    <t>ICC</t>
-  </si>
-  <si>
-    <t>Mixed</t>
-  </si>
-  <si>
-    <t>Coef.</t>
-  </si>
-  <si>
-    <t>0.01</t>
-  </si>
-  <si>
-    <t>-0.19</t>
-  </si>
-  <si>
-    <t>0.07</t>
-  </si>
-  <si>
-    <t>2.76</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>1690.23</t>
-  </si>
-  <si>
-    <t>(0.00, 0.01)</t>
-  </si>
-  <si>
-    <t>(-0.35, -0.04)</t>
-  </si>
-  <si>
-    <t>(0.06, 0.09)</t>
-  </si>
-  <si>
-    <t>(2.21, 3.32)</t>
-  </si>
-  <si>
-    <t>(0.00, 0.12)</t>
-  </si>
-  <si>
-    <t>(0.85, 1.07)</t>
-  </si>
-  <si>
-    <t>0.010</t>
-  </si>
-  <si>
-    <t>0.016</t>
-  </si>
-  <si>
-    <t>Table 5a. CDISC-Format Regression Output</t>
-  </si>
-  <si>
-    <t>CDISC</t>
-  </si>
-  <si>
-    <t>1.0014</t>
-  </si>
-  <si>
-    <t>0.9930</t>
-  </si>
-  <si>
-    <t>1.0190</t>
-  </si>
-  <si>
-    <t>1.0871</t>
-  </si>
-  <si>
-    <t>1.0082</t>
-  </si>
-  <si>
-    <t>1.0973</t>
-  </si>
-  <si>
-    <t>(0.9989, 1.0038)</t>
-  </si>
-  <si>
-    <t>(0.9291, 1.0613)</t>
-  </si>
-  <si>
-    <t>(0.9379, 1.1072)</t>
-  </si>
-  <si>
-    <t>(0.9988, 1.1832)</t>
-  </si>
-  <si>
-    <t>(0.9440, 1.0768)</t>
-  </si>
-  <si>
-    <t>(1.0275, 1.1718)</t>
-  </si>
-  <si>
-    <t>Table 5b. Poisson Regression -- Incidence Rate Ratios</t>
-  </si>
-  <si>
-    <t>Poisson</t>
-  </si>
-  <si>
-    <t>IRR</t>
-  </si>
-  <si>
-    <t>1.03</t>
-  </si>
-  <si>
-    <t>1.27</t>
+    <t>1.21</t>
+  </si>
+  <si>
+    <t>1.24</t>
   </si>
   <si>
     <t>1.22</t>
   </si>
   <si>
-    <t>21215.80</t>
-  </si>
-  <si>
-    <t>(0.97, 1.09)</t>
-  </si>
-  <si>
-    <t>(1.21, 1.35)</t>
-  </si>
-  <si>
-    <t>(1.15, 1.28)</t>
+    <t>1.23</t>
+  </si>
+  <si>
+    <t>(0.70, 3.20)</t>
+  </si>
+  <si>
+    <t>(0.58, 2.53)</t>
+  </si>
+  <si>
+    <t>(0.59, 2.59)</t>
+  </si>
+  <si>
+    <t>(0.77, 1.92)</t>
+  </si>
+  <si>
+    <t>(0.79, 1.91)</t>
   </si>
   <si>
     <t>0.30</t>
   </si>
   <si>
-    <t>0.019</t>
-  </si>
-  <si>
-    <t>0.72</t>
-  </si>
-  <si>
-    <t>Table 5c. GEE Models -- QICu for Model Comparison</t>
-  </si>
-  <si>
-    <t>Age in current year</t>
-  </si>
-  <si>
-    <t>Current grade completed</t>
-  </si>
-  <si>
-    <t>1 if not SMSA</t>
-  </si>
-  <si>
-    <t>1 if south</t>
-  </si>
-  <si>
-    <t>Race black</t>
-  </si>
-  <si>
-    <t>QICu</t>
-  </si>
-  <si>
-    <t>Base mean model</t>
-  </si>
-  <si>
-    <t>0.88</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>26,200</t>
-  </si>
-  <si>
-    <t>4,434</t>
-  </si>
-  <si>
-    <t>27142.20</t>
-  </si>
-  <si>
-    <t>(1.01, 1.01)</t>
-  </si>
-  <si>
-    <t>(1.04, 1.09)</t>
-  </si>
-  <si>
-    <t>(0.80, 0.97)</t>
-  </si>
-  <si>
-    <t>(0.51, 0.62)</t>
-  </si>
-  <si>
-    <t>0.009</t>
-  </si>
-  <si>
-    <t>Adjusted mean model</t>
-  </si>
-  <si>
-    <t>1.08</t>
-  </si>
-  <si>
-    <t>0.95</t>
-  </si>
-  <si>
-    <t>0.49</t>
-  </si>
-  <si>
-    <t>2.23</t>
-  </si>
-  <si>
-    <t>26596.04</t>
-  </si>
-  <si>
-    <t>(1.06, 1.11)</t>
-  </si>
-  <si>
-    <t>(0.86, 1.04)</t>
-  </si>
-  <si>
-    <t>(0.44, 0.54)</t>
-  </si>
-  <si>
-    <t>(1.97, 2.53)</t>
-  </si>
-  <si>
-    <t>0.26</t>
-  </si>
-  <si>
-    <t>Table 5d. Logistic Regression with Advanced Formatting</t>
-  </si>
-  <si>
-    <t>Marital status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Single</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Married</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Divorced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Widowed</t>
-  </si>
-  <si>
-    <t>Advanced</t>
-  </si>
-  <si>
-    <t>0.91</t>
-  </si>
-  <si>
-    <t>0.92</t>
-  </si>
-  <si>
-    <t>1.14</t>
-  </si>
-  <si>
-    <t>(0.96, 1.10)</t>
-  </si>
-  <si>
-    <t>(1.00, 1.01)</t>
-  </si>
-  <si>
-    <t>(0.96, 1.14)</t>
-  </si>
-  <si>
-    <t>(0.96, 1.15)</t>
-  </si>
-  <si>
-    <t>(0.84, 0.99)</t>
-  </si>
-  <si>
-    <t>(0.83, 1.01)</t>
-  </si>
-  <si>
-    <t>(0.87, 1.07)</t>
-  </si>
-  <si>
-    <t>(1.03, 1.18)</t>
-  </si>
-  <si>
-    <t>(0.93, 1.07)</t>
-  </si>
-  <si>
-    <t>(1.06, 1.23)</t>
-  </si>
-  <si>
-    <t>0.37</t>
-  </si>
-  <si>
-    <t>0.034</t>
-  </si>
-  <si>
-    <t>0.86</t>
-  </si>
-  <si>
-    <t>0.28</t>
-  </si>
-  <si>
-    <t>0.028</t>
-  </si>
-  <si>
-    <t>0.085</t>
-  </si>
-  <si>
-    <t>0.50</t>
-  </si>
-  <si>
-    <t>0.007</t>
+    <t>0.61</t>
   </si>
   <si>
     <t>0.39</t>
   </si>
   <si>
-    <t>Table 5e. Selected Covariates (keep/drop demo)</t>
-  </si>
-  <si>
-    <t>Selected</t>
-  </si>
-  <si>
-    <t>1.00*</t>
-  </si>
-  <si>
-    <t>1.10**</t>
-  </si>
-  <si>
-    <t>0.038</t>
-  </si>
-  <si>
-    <t>0.85</t>
-  </si>
-  <si>
-    <t>0.008</t>
-  </si>
-  <si>
-    <t>Selected covariates from full model. * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001</t>
-  </si>
-  <si>
-    <t>Table 5f. Logistic Model (Confounders Suppressed)</t>
-  </si>
-  <si>
-    <t>Adjusted</t>
-  </si>
-  <si>
-    <t>0.87</t>
-  </si>
-  <si>
-    <t>0.40</t>
-  </si>
-  <si>
-    <t>Model adjusted for age, sex, and education (coefficients suppressed).</t>
-  </si>
-  <si>
-    <t>Table 5g. Logistic Regression with Custom Summary Rows</t>
-  </si>
-  <si>
-    <t>P for trend</t>
-  </si>
-  <si>
-    <t>P for interaction</t>
-  </si>
-  <si>
-    <t>Model 1</t>
-  </si>
-  <si>
-    <t>1.12**</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>0.15</t>
-  </si>
-  <si>
-    <t>(1.04, 1.19)</t>
-  </si>
-  <si>
-    <t>(0.95, 1.08)</t>
-  </si>
-  <si>
-    <t>0.38</t>
-  </si>
-  <si>
-    <t>0.83</t>
-  </si>
-  <si>
-    <t>0.002</t>
-  </si>
-  <si>
-    <t>0.75</t>
-  </si>
-  <si>
-    <t>Custom rows appended below model estimates. * p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001</t>
+    <t>Regions with fewer than 15 events are not estimated (–).</t>
   </si>
 </sst>
 </file>
@@ -891,7 +1133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -1008,6 +1250,39 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1023,6 +1298,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="general" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="0"/>
     </xf>
@@ -1055,6 +1333,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="0"/>
@@ -1141,7 +1422,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -1158,7 +1439,7 @@
         <v>23</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -1175,7 +1456,7 @@
         <v>24</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -1226,7 +1507,7 @@
         <v>25</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -1237,13 +1518,13 @@
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -1254,13 +1535,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -1271,13 +1552,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -1288,13 +1569,13 @@
         <v>10</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -1308,10 +1589,10 @@
         <v>21</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1383,7 +1664,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -1391,33 +1672,33 @@
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>137</v>
+        <v>14</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>197</v>
+      <c r="C5" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="6">
@@ -1428,13 +1709,13 @@
         <v>3</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>27</v>
+        <v>190</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7">
@@ -1479,13 +1760,13 @@
         <v>6</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10">
@@ -1496,13 +1777,13 @@
         <v>7</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1550,10 +1831,10 @@
         <v>183</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14">
@@ -1567,10 +1848,10 @@
         <v>184</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15">
@@ -1581,13 +1862,13 @@
         <v>181</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>38</v>
+        <v>185</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1879,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17">
@@ -1615,13 +1896,13 @@
         <v>9</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>15</v>
+        <v>186</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>155</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18">
@@ -1632,13 +1913,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -1649,13 +1930,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -1682,7 +1963,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="18" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>1</v>
@@ -1705,7 +1986,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>1</v>
@@ -1728,7 +2009,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -1736,16 +2017,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>137</v>
+        <v>14</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5">
@@ -1756,13 +2037,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>187</v>
+        <v>84</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6">
@@ -1773,13 +2054,13 @@
         <v>3</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>27</v>
+        <v>190</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>210</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -1790,10 +2071,10 @@
         <v>8</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>211</v>
@@ -1876,7 +2157,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -1884,16 +2165,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>137</v>
+        <v>14</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5">
@@ -1938,10 +2219,10 @@
         <v>8</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>211</v>
@@ -1955,10 +2236,10 @@
         <v>9</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>15</v>
+        <v>186</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>24</v>
+        <v>196</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>215</v>
@@ -1972,13 +2253,13 @@
         <v>10</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -1989,10 +2270,10 @@
         <v>11</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>216</v>
@@ -2029,178 +2310,178 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="B1" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="60" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="59" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="D2" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="43" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="57" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="57" t="s">
+      <c r="D3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="58" t="s">
-        <v>31</v>
+      <c r="E3" s="15" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="53" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="47" t="s">
-        <v>137</v>
-      </c>
-      <c r="D4" s="47" t="s">
-        <v>186</v>
-      </c>
-      <c r="E4" s="48" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="53" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="47" t="s">
-        <v>207</v>
-      </c>
-      <c r="D5" s="47" t="s">
-        <v>187</v>
-      </c>
-      <c r="E5" s="48" t="s">
+      <c r="E7" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="53" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>222</v>
-      </c>
-      <c r="D7" s="47" t="s">
-        <v>225</v>
-      </c>
-      <c r="E7" s="48" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="47" t="s">
-        <v>226</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="55" t="s">
-        <v>219</v>
-      </c>
-      <c r="C9" s="46" t="s">
-        <v>223</v>
-      </c>
-      <c r="D9" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="52" t="s">
+      <c r="D9" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="54" t="s">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="D10" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="50" t="s">
+      <c r="D10" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="40" t="s">
-        <v>231</v>
+      <c r="B11" s="39" t="s">
+        <v>233</v>
       </c>
       <c r="C11" s="0"/>
       <c r="D11" s="0"/>
@@ -2213,6 +2494,1167 @@
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="B11:E11"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="28.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="7.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="16.2109375" style="1" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="1" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C2:E2"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="28.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="19.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="9.7109375" style="1" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="49" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>257</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>262</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="10.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="10.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="17.2109375" style="1" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="true" ht="30" customHeight="true">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>267</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C2:C2"/>
+    <mergeCell ref="D2:D2"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="28.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="12.2109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="12.2109375" style="1" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="1" customWidth="true"/>
+    <col min="6" max="6" width="12.2109375" style="1" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>228</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="19.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="7.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="12.2109375" style="1" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="1" customWidth="true"/>
+    <col min="6" max="6" width="7.7109375" style="1" customWidth="true"/>
+    <col min="7" max="7" width="12.2109375" style="1" customWidth="true"/>
+    <col min="8" max="8" width="7.7109375" style="1" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="74" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="73" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="72" t="s">
+        <v>264</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="72" t="s">
+        <v>214</v>
+      </c>
+      <c r="G2" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="54" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="70" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="71" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="70" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="71" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="65" t="s">
+        <v>276</v>
+      </c>
+      <c r="C5" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="65" t="s">
+        <v>277</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>285</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>291</v>
+      </c>
+      <c r="E6" s="60" t="s">
+        <v>294</v>
+      </c>
+      <c r="F6" s="59" t="s">
+        <v>297</v>
+      </c>
+      <c r="G6" s="59" t="s">
+        <v>302</v>
+      </c>
+      <c r="H6" s="60" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="65" t="s">
+        <v>278</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" s="59" t="s">
+        <v>292</v>
+      </c>
+      <c r="E7" s="60" t="s">
+        <v>295</v>
+      </c>
+      <c r="F7" s="59" t="s">
+        <v>298</v>
+      </c>
+      <c r="G7" s="59" t="s">
+        <v>303</v>
+      </c>
+      <c r="H7" s="60" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="65" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8" s="68" t="s">
+        <v>286</v>
+      </c>
+      <c r="D8" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="68" t="s">
+        <v>286</v>
+      </c>
+      <c r="G8" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="65" t="s">
+        <v>280</v>
+      </c>
+      <c r="C9" s="59" t="s">
+        <v>287</v>
+      </c>
+      <c r="D9" s="59" t="s">
+        <v>293</v>
+      </c>
+      <c r="E9" s="60" t="s">
+        <v>296</v>
+      </c>
+      <c r="F9" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="G9" s="59" t="s">
+        <v>304</v>
+      </c>
+      <c r="H9" s="60" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="65" t="s">
+        <v>281</v>
+      </c>
+      <c r="C10" s="68" t="s">
+        <v>286</v>
+      </c>
+      <c r="D10" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="68" t="s">
+        <v>286</v>
+      </c>
+      <c r="G10" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="59" t="s">
+        <v>300</v>
+      </c>
+      <c r="G11" s="59" t="s">
+        <v>305</v>
+      </c>
+      <c r="H11" s="60" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="65" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="59" t="s">
+        <v>301</v>
+      </c>
+      <c r="G12" s="59" t="s">
+        <v>306</v>
+      </c>
+      <c r="H12" s="60" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="67" t="s">
+        <v>282</v>
+      </c>
+      <c r="C13" s="58" t="s">
+        <v>288</v>
+      </c>
+      <c r="D13" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="58" t="s">
+        <v>288</v>
+      </c>
+      <c r="G13" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="64" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="65" t="s">
+        <v>283</v>
+      </c>
+      <c r="C14" s="56" t="s">
+        <v>289</v>
+      </c>
+      <c r="D14" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="56" t="s">
+        <v>289</v>
+      </c>
+      <c r="G14" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="66" t="s">
+        <v>284</v>
+      </c>
+      <c r="C15" s="57" t="s">
+        <v>290</v>
+      </c>
+      <c r="D15" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="57" t="s">
+        <v>290</v>
+      </c>
+      <c r="G15" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="62" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="51" t="s">
+        <v>310</v>
+      </c>
+      <c r="C16" s="0"/>
+      <c r="D16" s="0"/>
+      <c r="E16" s="0"/>
+      <c r="F16" s="0"/>
+      <c r="G16" s="0"/>
+      <c r="H16" s="0"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="B16:H16"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -2230,7 +3672,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="18" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>1</v>
@@ -2250,7 +3692,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>1</v>
@@ -2264,10 +3706,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -2278,10 +3720,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -2292,10 +3734,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -2334,10 +3776,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -2348,10 +3790,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -2362,10 +3804,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -2376,10 +3818,10 @@
         <v>9</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -2390,10 +3832,10 @@
         <v>10</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -2404,10 +3846,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2432,7 +3874,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="18" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>1</v>
@@ -2452,7 +3894,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>1</v>
@@ -2550,10 +3992,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -2564,10 +4006,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -2578,10 +4020,10 @@
         <v>9</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -2592,10 +4034,10 @@
         <v>10</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -2609,7 +4051,7 @@
         <v>21</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2641,7 +4083,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>1</v>
@@ -2682,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>1</v>
@@ -2691,7 +4133,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>1</v>
@@ -2700,7 +4142,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>1</v>
@@ -2723,7 +4165,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3" s="14" t="s">
         <v>13</v>
@@ -2732,7 +4174,7 @@
         <v>22</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>13</v>
@@ -2741,7 +4183,7 @@
         <v>22</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -2752,13 +4194,13 @@
         <v>2</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>14</v>
@@ -2767,7 +4209,7 @@
         <v>23</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>14</v>
@@ -2776,7 +4218,7 @@
         <v>23</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -2787,13 +4229,13 @@
         <v>3</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>15</v>
@@ -2802,7 +4244,7 @@
         <v>24</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>15</v>
@@ -2811,7 +4253,7 @@
         <v>24</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -2907,7 +4349,7 @@
         <v>25</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>17</v>
@@ -2916,7 +4358,7 @@
         <v>25</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -2936,22 +4378,22 @@
         <v>1</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -2971,22 +4413,22 @@
         <v>1</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -3006,22 +4448,22 @@
         <v>1</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -3050,13 +4492,13 @@
         <v>1</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -3088,10 +4530,10 @@
         <v>21</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3099,10 +4541,10 @@
         <v>1</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D14" s="22" t="s">
         <v>1</v>
@@ -3111,7 +4553,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G14" s="22" t="s">
         <v>1</v>
@@ -3120,7 +4562,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J14" s="22" t="s">
         <v>1</v>
@@ -3134,10 +4576,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>1</v>
@@ -3146,7 +4588,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>1</v>
@@ -3155,7 +4597,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>1</v>
@@ -3169,10 +4611,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>1</v>
@@ -3181,7 +4623,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>1</v>
@@ -3190,7 +4632,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>1</v>
@@ -3234,7 +4676,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>1</v>
@@ -3257,7 +4699,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>1</v>
@@ -3274,13 +4716,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -3288,10 +4730,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>83</v>
@@ -3308,13 +4750,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
@@ -3325,13 +4767,13 @@
         <v>3</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
@@ -3376,13 +4818,13 @@
         <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -3393,13 +4835,13 @@
         <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -3416,7 +4858,7 @@
         <v>87</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -3433,7 +4875,7 @@
         <v>88</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -3450,7 +4892,7 @@
         <v>89</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3458,10 +4900,10 @@
         <v>1</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D14" s="22" t="s">
         <v>1</v>
@@ -3475,7 +4917,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>82</v>
@@ -3558,7 +5000,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -3572,10 +5014,10 @@
         <v>105</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5">
@@ -3589,10 +5031,10 @@
         <v>106</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6">
@@ -3606,10 +5048,10 @@
         <v>107</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -3623,10 +5065,10 @@
         <v>108</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -3640,7 +5082,7 @@
         <v>105</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E8" s="23" t="s">
         <v>1</v>
@@ -3654,10 +5096,10 @@
         <v>100</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>1</v>
@@ -3668,10 +5110,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D10" s="22" t="s">
         <v>1</v>
@@ -3688,7 +5130,7 @@
         <v>101</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>1</v>
@@ -3702,10 +5144,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>1</v>
@@ -3722,7 +5164,7 @@
         <v>102</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>1</v>
@@ -3757,7 +5199,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="18" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>1</v>
@@ -3780,7 +5222,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>1</v>
@@ -3803,7 +5245,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -3814,13 +5256,13 @@
         <v>2</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -3831,13 +5273,13 @@
         <v>3</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -3882,13 +5324,13 @@
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
@@ -3899,13 +5341,13 @@
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -3916,13 +5358,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -3933,13 +5375,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -3947,10 +5389,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D12" s="26" t="s">
         <v>1</v>
@@ -3983,7 +5425,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>1</v>
@@ -4006,7 +5448,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>1</v>
@@ -4023,13 +5465,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -4037,16 +5479,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5">
@@ -4057,13 +5499,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6">
@@ -4074,13 +5516,13 @@
         <v>3</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7">
@@ -4091,13 +5533,13 @@
         <v>8</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -4108,13 +5550,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -4122,10 +5564,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D9" s="22" t="s">
         <v>1</v>
@@ -4139,10 +5581,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>1</v>
@@ -4178,7 +5620,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>1</v>
@@ -4210,7 +5652,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>1</v>
@@ -4219,7 +5661,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>1</v>
@@ -4242,7 +5684,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3" s="14" t="s">
         <v>13</v>
@@ -4251,7 +5693,7 @@
         <v>22</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -4259,25 +5701,25 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -4285,25 +5727,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>171</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -4311,19 +5753,19 @@
         <v>1</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>167</v>
+        <v>17</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>172</v>
@@ -4337,16 +5779,16 @@
         <v>1</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>168</v>
@@ -4355,7 +5797,7 @@
         <v>173</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -4363,7 +5805,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>1</v>
@@ -4381,7 +5823,7 @@
         <v>174</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -4389,10 +5831,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D9" s="22" t="s">
         <v>1</v>
@@ -4401,7 +5843,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G9" s="22" t="s">
         <v>1</v>
@@ -4418,7 +5860,7 @@
         <v>101</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>1</v>
@@ -4427,7 +5869,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>1</v>
@@ -4441,10 +5883,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>1</v>

--- a/tabtools/demo/demo_regtab.xlsx
+++ b/tabtools/demo/demo_regtab.xlsx
@@ -794,19 +794,19 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>1.09 (1.02, 1.17)</t>
-  </si>
-  <si>
-    <t>1.00 (1.00, 1.00)</t>
-  </si>
-  <si>
-    <t>1.01 (0.94, 1.08)</t>
-  </si>
-  <si>
-    <t>0.95 (0.87, 1.04)</t>
-  </si>
-  <si>
-    <t>1.00 (0.93, 1.08)</t>
+    <t>1.092 (1.018, 1.171)</t>
+  </si>
+  <si>
+    <t>1.002 (1.000, 1.005)</t>
+  </si>
+  <si>
+    <t>1.011 (0.944, 1.083)</t>
+  </si>
+  <si>
+    <t>0.949 (0.870, 1.036)</t>
+  </si>
+  <si>
+    <t>1.000 (0.925, 1.081)</t>
   </si>
   <si>
     <t>0.014</t>
@@ -2730,7 +2730,7 @@
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
     <col min="2" max="2" width="28.7109375" style="1" customWidth="true"/>
-    <col min="3" max="3" width="19.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="21.7109375" style="1" customWidth="true"/>
     <col min="4" max="4" width="9.7109375" style="1" customWidth="true"/>
   </cols>
   <sheetData>
